--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -160,12 +160,12 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -187,15 +187,15 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Utsikten</t>
   </si>
   <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -223,13 +223,13 @@
     <t>Haka</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
     <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>Värnamo</t>
   </si>
   <si>
     <t>Huracán</t>
@@ -908,40 +908,40 @@
         <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T3">
         <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AA3">
         <v>4.4</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD3">
         <v>2.38</v>
@@ -950,16 +950,16 @@
         <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AI3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="s">
         <v>80</v>
@@ -1006,22 +1006,22 @@
         <v>79</v>
       </c>
       <c r="L4">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="P4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1042,28 +1042,28 @@
         <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD4">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AE4">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AF4">
         <v>1.57</v>
@@ -1072,10 +1072,10 @@
         <v>2.25</v>
       </c>
       <c r="AH4">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>80</v>
@@ -1095,7 +1095,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>54</v>
@@ -1122,40 +1122,40 @@
         <v>79</v>
       </c>
       <c r="L5">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="M5">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="P5">
-        <v>13.25</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1164,34 +1164,34 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AI5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
         <v>80</v>
@@ -1238,76 +1238,76 @@
         <v>79</v>
       </c>
       <c r="L6">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="M6">
         <v>3.56</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
-        <v>11</v>
+        <v>13.25</v>
       </c>
       <c r="Q6">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>11</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA6">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AB6">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD6">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AE6">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH6">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AI6">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
         <v>80</v>
@@ -1470,13 +1470,13 @@
         <v>79</v>
       </c>
       <c r="L8">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M8">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N8">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O8">
         <v>1.95</v>
@@ -1488,34 +1488,34 @@
         <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="U8">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V8">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
         <v>1.05</v>
       </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
       <c r="Y8">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z8">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AA8">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AB8">
         <v>2.25</v>
@@ -1524,22 +1524,22 @@
         <v>1.53</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="s">
         <v>80</v>
@@ -1586,13 +1586,13 @@
         <v>79</v>
       </c>
       <c r="L9">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="M9">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
         <v>1.78</v>
@@ -1604,34 +1604,34 @@
         <v>2.35</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S9">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
         <v>1.06</v>
       </c>
-      <c r="X9">
-        <v>1.07</v>
-      </c>
       <c r="Y9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB9">
         <v>2.15</v>
@@ -1640,22 +1640,22 @@
         <v>1.57</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AH9">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>80</v>
@@ -2068,58 +2068,58 @@
         <v>2.88</v>
       </c>
       <c r="R13">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S13">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V13">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AA13">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AD13">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI13">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AJ13" t="s">
         <v>80</v>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -160,12 +160,12 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -187,33 +187,33 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
     <t>Utsikten</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Náutico</t>
+  </si>
+  <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Náutico</t>
-  </si>
-  <si>
     <t>Huachipato</t>
   </si>
   <si>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
@@ -223,31 +223,31 @@
     <t>Haka</t>
   </si>
   <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Caxias</t>
-  </si>
-  <si>
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
     <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Deportivo Riestra</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
@@ -1006,76 +1006,76 @@
         <v>79</v>
       </c>
       <c r="L4">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="M4">
         <v>3.56</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P4">
-        <v>11</v>
+        <v>13.25</v>
       </c>
       <c r="Q4">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA4">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC4">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD4">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AE4">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH4">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>80</v>
@@ -1122,22 +1122,22 @@
         <v>79</v>
       </c>
       <c r="L5">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="M5">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="N5">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="O5">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="P5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1158,28 +1158,28 @@
         <v>1.13</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA5">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD5">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AE5">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AF5">
         <v>1.57</v>
@@ -1188,10 +1188,10 @@
         <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AI5">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
         <v>80</v>
@@ -1211,7 +1211,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>54</v>
@@ -1238,40 +1238,40 @@
         <v>79</v>
       </c>
       <c r="L6">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="M6">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="O6">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="P6">
-        <v>13.25</v>
+        <v>16</v>
       </c>
       <c r="Q6">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1280,34 +1280,34 @@
         <v>11</v>
       </c>
       <c r="Z6">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA6">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD6">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH6">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AI6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>80</v>
@@ -1470,34 +1470,34 @@
         <v>79</v>
       </c>
       <c r="L8">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="M8">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N8">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R8">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="T8">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1506,40 +1506,40 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="Z8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AB8">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD8">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH8">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="s">
         <v>80</v>
@@ -1586,34 +1586,34 @@
         <v>79</v>
       </c>
       <c r="L9">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="M9">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="O9">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1622,40 +1622,40 @@
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AA9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD9">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AG9">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>80</v>
@@ -1818,76 +1818,76 @@
         <v>79</v>
       </c>
       <c r="L11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="s">
         <v>80</v>
@@ -1934,76 +1934,76 @@
         <v>79</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>80</v>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -160,12 +160,15 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -187,24 +190,27 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
     <t>Huachipato</t>
   </si>
   <si>
@@ -223,22 +229,25 @@
     <t>Haka</t>
   </si>
   <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Caxias</t>
-  </si>
-  <si>
-    <t>Guarani</t>
   </si>
   <si>
     <t>O'Higgins</t>
@@ -620,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL13"/>
+  <dimension ref="A1:AL14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -750,13 +759,13 @@
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -771,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L2">
         <v>2.72</v>
@@ -846,10 +855,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL2" s="3">
         <v>45859.25</v>
@@ -866,13 +875,13 @@
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -887,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L3">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="M3">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N3">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="O3">
         <v>2.2</v>
@@ -908,64 +917,64 @@
         <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V3">
         <v>5.5</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="Z3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AA3">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AC3">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AD3">
+        <v>2.67</v>
+      </c>
+      <c r="AE3">
+        <v>1.47</v>
+      </c>
+      <c r="AF3">
+        <v>1.57</v>
+      </c>
+      <c r="AG3">
         <v>2.38</v>
       </c>
-      <c r="AE3">
-        <v>1.53</v>
-      </c>
-      <c r="AF3">
-        <v>1.53</v>
-      </c>
-      <c r="AG3">
-        <v>2.4</v>
-      </c>
       <c r="AH3">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="AI3">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AJ3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL3" s="3">
         <v>45859.5</v>
@@ -982,13 +991,13 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1003,85 +1012,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL4" s="3">
         <v>45859.58333333334</v>
@@ -1098,13 +1107,13 @@
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1119,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L5">
         <v>2.04</v>
@@ -1194,10 +1203,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL5" s="3">
         <v>45859.58333333334</v>
@@ -1211,16 +1220,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1235,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L6">
         <v>2.56</v>
@@ -1310,10 +1319,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL6" s="3">
         <v>45859.58333333334</v>
@@ -1324,19 +1333,19 @@
         <v>45859</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1351,88 +1360,88 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L7">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="N7">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>5.5</v>
+        <v>13.25</v>
       </c>
       <c r="Q7">
+        <v>2.63</v>
+      </c>
+      <c r="R7">
+        <v>1.33</v>
+      </c>
+      <c r="S7">
+        <v>3.25</v>
+      </c>
+      <c r="T7">
+        <v>2.63</v>
+      </c>
+      <c r="U7">
+        <v>1.44</v>
+      </c>
+      <c r="V7">
+        <v>6.5</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>1.2</v>
+      </c>
+      <c r="AA7">
+        <v>3.74</v>
+      </c>
+      <c r="AB7">
+        <v>1.77</v>
+      </c>
+      <c r="AC7">
+        <v>1.93</v>
+      </c>
+      <c r="AD7">
         <v>2.75</v>
       </c>
-      <c r="R7">
-        <v>1.62</v>
-      </c>
-      <c r="S7">
-        <v>2.2</v>
-      </c>
-      <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
-        <v>1.22</v>
-      </c>
-      <c r="V7">
-        <v>13</v>
-      </c>
-      <c r="W7">
-        <v>1.04</v>
-      </c>
-      <c r="X7">
-        <v>1.12</v>
-      </c>
-      <c r="Y7">
-        <v>5.75</v>
-      </c>
-      <c r="Z7">
-        <v>1.6</v>
-      </c>
-      <c r="AA7">
-        <v>2.2</v>
-      </c>
-      <c r="AB7">
-        <v>2.88</v>
-      </c>
-      <c r="AC7">
-        <v>1.4</v>
-      </c>
-      <c r="AD7">
-        <v>6</v>
-      </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AF7">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AH7">
-        <v>11</v>
+        <v>5.15</v>
       </c>
       <c r="AI7">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL7" s="3">
-        <v>45859.79166666666</v>
+        <v>45859.58333333334</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1440,19 +1449,19 @@
         <v>45859</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1467,88 +1476,88 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L8">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M8">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O8">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="P8">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q8">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y8">
+        <v>5.75</v>
+      </c>
+      <c r="Z8">
+        <v>1.6</v>
+      </c>
+      <c r="AA8">
+        <v>2.2</v>
+      </c>
+      <c r="AB8">
+        <v>2.88</v>
+      </c>
+      <c r="AC8">
+        <v>1.4</v>
+      </c>
+      <c r="AD8">
         <v>6</v>
       </c>
-      <c r="Z8">
-        <v>1.5</v>
-      </c>
-      <c r="AA8">
-        <v>2.4</v>
-      </c>
-      <c r="AB8">
-        <v>2.15</v>
-      </c>
-      <c r="AC8">
-        <v>1.57</v>
-      </c>
-      <c r="AD8">
-        <v>5.25</v>
-      </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG8">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL8" s="3">
-        <v>45859.8125</v>
+        <v>45859.79166666666</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1559,16 +1568,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1583,16 +1592,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L9">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M9">
         <v>2.75</v>
       </c>
       <c r="N9">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
         <v>1.95</v>
@@ -1604,52 +1613,52 @@
         <v>2.2</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="U9">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
         <v>10</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="Z9">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AA9">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC9">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AD9">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH9">
         <v>11.5</v>
@@ -1658,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL9" s="3">
         <v>45859.8125</v>
@@ -1672,19 +1681,19 @@
         <v>45859</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1699,88 +1708,88 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N10">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AA10">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AC10">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AD10">
-        <v>3.65</v>
+        <v>5.25</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AH10">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AI10">
         <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL10" s="3">
-        <v>45859.83333333334</v>
+        <v>45859.8125</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1788,19 +1797,19 @@
         <v>45859</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1815,88 +1824,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL11" s="3">
-        <v>45859.88541666666</v>
+        <v>45859.83333333334</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1907,16 +1916,16 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1931,85 +1940,85 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L12">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL12" s="3">
         <v>45859.88541666666</v>
@@ -2020,19 +2029,19 @@
         <v>45859</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2047,87 +2056,203 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L13">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="M13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
         <v>4.5</v>
       </c>
       <c r="O13">
+        <v>1.53</v>
+      </c>
+      <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>1.44</v>
+      </c>
+      <c r="S13">
+        <v>2.63</v>
+      </c>
+      <c r="T13">
+        <v>3.4</v>
+      </c>
+      <c r="U13">
+        <v>1.3</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.08</v>
+      </c>
+      <c r="Y13">
+        <v>7.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.42</v>
+      </c>
+      <c r="AA13">
+        <v>2.85</v>
+      </c>
+      <c r="AB13">
+        <v>2.25</v>
+      </c>
+      <c r="AC13">
+        <v>1.62</v>
+      </c>
+      <c r="AD13">
+        <v>4.2</v>
+      </c>
+      <c r="AE13">
+        <v>1.22</v>
+      </c>
+      <c r="AF13">
+        <v>2.05</v>
+      </c>
+      <c r="AG13">
+        <v>1.7</v>
+      </c>
+      <c r="AH13">
+        <v>8.5</v>
+      </c>
+      <c r="AI13">
+        <v>1.06</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>45859.88541666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="2">
+        <v>45859</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14">
+        <v>1.9</v>
+      </c>
+      <c r="M14">
+        <v>3.26</v>
+      </c>
+      <c r="N14">
+        <v>3.54</v>
+      </c>
+      <c r="O14">
         <v>1.57</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>8.9</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>2.88</v>
       </c>
-      <c r="R13">
+      <c r="R14">
         <v>1.38</v>
       </c>
-      <c r="S13">
+      <c r="S14">
         <v>2.8</v>
       </c>
-      <c r="T13">
-        <v>2.7</v>
-      </c>
-      <c r="U13">
+      <c r="T14">
+        <v>2.84</v>
+      </c>
+      <c r="U14">
         <v>1.4</v>
       </c>
-      <c r="V13">
-        <v>6</v>
-      </c>
-      <c r="W13">
-        <v>1.09</v>
-      </c>
-      <c r="X13">
-        <v>1.06</v>
-      </c>
-      <c r="Y13">
-        <v>10</v>
-      </c>
-      <c r="Z13">
-        <v>1.29</v>
-      </c>
-      <c r="AA13">
-        <v>3.5</v>
-      </c>
-      <c r="AB13">
-        <v>1.88</v>
-      </c>
-      <c r="AC13">
-        <v>1.82</v>
-      </c>
-      <c r="AD13">
-        <v>3.2</v>
-      </c>
-      <c r="AE13">
+      <c r="V14">
+        <v>6.5</v>
+      </c>
+      <c r="W14">
+        <v>1.08</v>
+      </c>
+      <c r="X14">
+        <v>1.05</v>
+      </c>
+      <c r="Y14">
+        <v>9</v>
+      </c>
+      <c r="Z14">
+        <v>1.24</v>
+      </c>
+      <c r="AA14">
+        <v>3.17</v>
+      </c>
+      <c r="AB14">
+        <v>1.91</v>
+      </c>
+      <c r="AC14">
+        <v>1.85</v>
+      </c>
+      <c r="AD14">
+        <v>3.28</v>
+      </c>
+      <c r="AE14">
         <v>1.3</v>
       </c>
-      <c r="AF13">
+      <c r="AF14">
         <v>1.8</v>
       </c>
-      <c r="AG13">
-        <v>2</v>
-      </c>
-      <c r="AH13">
-        <v>6</v>
-      </c>
-      <c r="AI13">
+      <c r="AG14">
+        <v>2.03</v>
+      </c>
+      <c r="AH14">
+        <v>6.5</v>
+      </c>
+      <c r="AI14">
         <v>1.11</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL13" s="3">
+      <c r="AJ14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45859.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -160,15 +160,15 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -190,18 +190,18 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>Huachipato</t>
   </si>
   <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
@@ -229,18 +229,18 @@
     <t>Haka</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
@@ -253,10 +253,10 @@
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
     <t>Deportivo Riestra</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
@@ -1015,76 +1015,76 @@
         <v>82</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>83</v>
@@ -1104,7 +1104,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -1131,76 +1131,76 @@
         <v>82</v>
       </c>
       <c r="L5">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="M5">
         <v>3.56</v>
       </c>
       <c r="N5">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P5">
-        <v>11</v>
+        <v>13.25</v>
       </c>
       <c r="Q5">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U5">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AB5">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD5">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AE5">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH5">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AI5">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="s">
         <v>83</v>
@@ -1220,7 +1220,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>55</v>
@@ -1247,76 +1247,76 @@
         <v>82</v>
       </c>
       <c r="L6">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="M6">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="N6">
-        <v>2.33</v>
+        <v>3.26</v>
       </c>
       <c r="O6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="Z6">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AA6">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
+        <v>2.75</v>
+      </c>
+      <c r="AC6">
+        <v>1.42</v>
+      </c>
+      <c r="AD6">
+        <v>5.25</v>
+      </c>
+      <c r="AE6">
+        <v>1.12</v>
+      </c>
+      <c r="AF6">
+        <v>2.1</v>
+      </c>
+      <c r="AG6">
         <v>1.6</v>
       </c>
-      <c r="AC6">
-        <v>2.1</v>
-      </c>
-      <c r="AD6">
-        <v>2.6</v>
-      </c>
-      <c r="AE6">
-        <v>1.39</v>
-      </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
-      <c r="AG6">
-        <v>2.25</v>
-      </c>
       <c r="AH6">
-        <v>4.95</v>
+        <v>10</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ6" t="s">
         <v>83</v>
@@ -1363,76 +1363,76 @@
         <v>82</v>
       </c>
       <c r="L7">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="M7">
         <v>3.56</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="P7">
-        <v>13.25</v>
+        <v>11</v>
       </c>
       <c r="Q7">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V7">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>11</v>
       </c>
       <c r="Z7">
+        <v>1.22</v>
+      </c>
+      <c r="AA7">
+        <v>4.33</v>
+      </c>
+      <c r="AB7">
+        <v>1.57</v>
+      </c>
+      <c r="AC7">
+        <v>2.25</v>
+      </c>
+      <c r="AD7">
+        <v>2.38</v>
+      </c>
+      <c r="AE7">
+        <v>1.58</v>
+      </c>
+      <c r="AF7">
+        <v>1.57</v>
+      </c>
+      <c r="AG7">
+        <v>2.25</v>
+      </c>
+      <c r="AH7">
+        <v>4.75</v>
+      </c>
+      <c r="AI7">
         <v>1.2</v>
-      </c>
-      <c r="AA7">
-        <v>3.74</v>
-      </c>
-      <c r="AB7">
-        <v>1.77</v>
-      </c>
-      <c r="AC7">
-        <v>1.93</v>
-      </c>
-      <c r="AD7">
-        <v>2.75</v>
-      </c>
-      <c r="AE7">
-        <v>1.35</v>
-      </c>
-      <c r="AF7">
-        <v>1.7</v>
-      </c>
-      <c r="AG7">
-        <v>2.05</v>
-      </c>
-      <c r="AH7">
-        <v>5.15</v>
-      </c>
-      <c r="AI7">
-        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
         <v>83</v>
@@ -1595,13 +1595,13 @@
         <v>82</v>
       </c>
       <c r="L9">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M9">
         <v>2.75</v>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O9">
         <v>1.95</v>
@@ -1622,7 +1622,7 @@
         <v>3.7</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1643,10 +1643,10 @@
         <v>2.28</v>
       </c>
       <c r="AB9">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AD9">
         <v>5.75</v>
@@ -1658,7 +1658,7 @@
         <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH9">
         <v>11.5</v>
@@ -1729,7 +1729,7 @@
         <v>2.35</v>
       </c>
       <c r="R10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S10">
         <v>2.25</v>
@@ -1741,7 +1741,7 @@
         <v>1.2</v>
       </c>
       <c r="V10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="W10">
         <v>1.02</v>
@@ -1753,16 +1753,16 @@
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AA10">
         <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AD10">
         <v>5.25</v>
@@ -1943,76 +1943,76 @@
         <v>82</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>83</v>
@@ -2059,76 +2059,76 @@
         <v>82</v>
       </c>
       <c r="L13">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="s">
         <v>83</v>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -205,12 +205,12 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Náutico</t>
+  </si>
+  <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Náutico</t>
-  </si>
-  <si>
     <t>Huachipato</t>
   </si>
   <si>
@@ -244,10 +244,10 @@
     <t>Huracán</t>
   </si>
   <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Guarani</t>
-  </si>
-  <si>
-    <t>Caxias</t>
   </si>
   <si>
     <t>O'Higgins</t>
@@ -899,13 +899,13 @@
         <v>82</v>
       </c>
       <c r="L3">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="M3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="O3">
         <v>2.2</v>
@@ -917,58 +917,58 @@
         <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
         <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
         <v>5.5</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Z3">
         <v>1.17</v>
       </c>
       <c r="AA3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AB3">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AC3">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD3">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="AE3">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH3">
-        <v>4.91</v>
+        <v>4.55</v>
       </c>
       <c r="AI3">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ3" t="s">
         <v>83</v>
@@ -1247,37 +1247,37 @@
         <v>82</v>
       </c>
       <c r="L6">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M6">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="N6">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T6">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -1286,34 +1286,34 @@
         <v>1.12</v>
       </c>
       <c r="Y6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z6">
         <v>1.57</v>
       </c>
       <c r="AA6">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB6">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AD6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG6">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI6">
         <v>1.02</v>
@@ -1595,76 +1595,76 @@
         <v>82</v>
       </c>
       <c r="L9">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="M9">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="N9">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="O9">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R9">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S9">
+        <v>2.25</v>
+      </c>
+      <c r="T9">
+        <v>3.6</v>
+      </c>
+      <c r="U9">
+        <v>1.2</v>
+      </c>
+      <c r="V9">
+        <v>10.5</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.06</v>
+      </c>
+      <c r="Y9">
+        <v>5.75</v>
+      </c>
+      <c r="Z9">
+        <v>1.55</v>
+      </c>
+      <c r="AA9">
         <v>2.3</v>
       </c>
-      <c r="T9">
-        <v>3.7</v>
-      </c>
-      <c r="U9">
-        <v>1.17</v>
-      </c>
-      <c r="V9">
-        <v>10</v>
-      </c>
-      <c r="W9">
+      <c r="AB9">
+        <v>2.15</v>
+      </c>
+      <c r="AC9">
+        <v>1.57</v>
+      </c>
+      <c r="AD9">
+        <v>5.25</v>
+      </c>
+      <c r="AE9">
+        <v>1.09</v>
+      </c>
+      <c r="AF9">
+        <v>2.25</v>
+      </c>
+      <c r="AG9">
+        <v>1.57</v>
+      </c>
+      <c r="AH9">
+        <v>7.6</v>
+      </c>
+      <c r="AI9">
         <v>1.04</v>
-      </c>
-      <c r="X9">
-        <v>1.07</v>
-      </c>
-      <c r="Y9">
-        <v>5.9</v>
-      </c>
-      <c r="Z9">
-        <v>1.58</v>
-      </c>
-      <c r="AA9">
-        <v>2.28</v>
-      </c>
-      <c r="AB9">
-        <v>2.25</v>
-      </c>
-      <c r="AC9">
-        <v>1.53</v>
-      </c>
-      <c r="AD9">
-        <v>5.75</v>
-      </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>2.05</v>
-      </c>
-      <c r="AG9">
-        <v>1.64</v>
-      </c>
-      <c r="AH9">
-        <v>11.5</v>
-      </c>
-      <c r="AI9">
-        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>83</v>
@@ -1711,76 +1711,76 @@
         <v>82</v>
       </c>
       <c r="L10">
-        <v>1.99</v>
+        <v>2.84</v>
       </c>
       <c r="M10">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="N10">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="P10">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S10">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="T10">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="U10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z10">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AA10">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD10">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG10">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH10">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
         <v>83</v>
@@ -2175,13 +2175,13 @@
         <v>82</v>
       </c>
       <c r="L14">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="M14">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="O14">
         <v>1.57</v>
@@ -2199,10 +2199,10 @@
         <v>2.8</v>
       </c>
       <c r="T14">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="U14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V14">
         <v>6.5</v>
@@ -2211,22 +2211,22 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14">
         <v>1.24</v>
       </c>
       <c r="AA14">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="AB14">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC14">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD14">
         <v>3.28</v>
@@ -2241,7 +2241,7 @@
         <v>2.03</v>
       </c>
       <c r="AH14">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AI14">
         <v>1.11</v>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -160,15 +160,15 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -190,18 +190,18 @@
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Utsikten</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
     <t>Agropecuario</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>Huachipato</t>
   </si>
   <si>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
@@ -229,18 +229,18 @@
     <t>Haka</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
@@ -253,10 +253,10 @@
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
     <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Deportivo Riestra</t>
   </si>
   <si>
     <t>Unión San Felipe</t>
@@ -899,13 +899,13 @@
         <v>82</v>
       </c>
       <c r="L3">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="M3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N3">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="O3">
         <v>2.2</v>
@@ -917,10 +917,10 @@
         <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T3">
         <v>2.3</v>
@@ -929,46 +929,46 @@
         <v>1.5</v>
       </c>
       <c r="V3">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>9</v>
       </c>
       <c r="Z3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA3">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AE3">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF3">
         <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AH3">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AI3">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ3" t="s">
         <v>83</v>
@@ -1015,22 +1015,22 @@
         <v>82</v>
       </c>
       <c r="L4">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="P4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1051,28 +1051,28 @@
         <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD4">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AE4">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AF4">
         <v>1.57</v>
@@ -1081,10 +1081,10 @@
         <v>2.25</v>
       </c>
       <c r="AH4">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>83</v>
@@ -1104,7 +1104,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -1247,76 +1247,76 @@
         <v>82</v>
       </c>
       <c r="L6">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="M6">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="O6">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q6">
+        <v>1.91</v>
+      </c>
+      <c r="R6">
+        <v>1.3</v>
+      </c>
+      <c r="S6">
+        <v>3.4</v>
+      </c>
+      <c r="T6">
         <v>2.5</v>
       </c>
-      <c r="R6">
-        <v>1.65</v>
-      </c>
-      <c r="S6">
-        <v>2.16</v>
-      </c>
-      <c r="T6">
-        <v>3.9</v>
-      </c>
       <c r="U6">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="Z6">
+        <v>1.15</v>
+      </c>
+      <c r="AA6">
+        <v>4.25</v>
+      </c>
+      <c r="AB6">
+        <v>1.6</v>
+      </c>
+      <c r="AC6">
+        <v>2.1</v>
+      </c>
+      <c r="AD6">
+        <v>2.6</v>
+      </c>
+      <c r="AE6">
+        <v>1.39</v>
+      </c>
+      <c r="AF6">
         <v>1.57</v>
       </c>
-      <c r="AA6">
-        <v>2.31</v>
-      </c>
-      <c r="AB6">
-        <v>2.66</v>
-      </c>
-      <c r="AC6">
-        <v>1.38</v>
-      </c>
-      <c r="AD6">
-        <v>5.5</v>
-      </c>
-      <c r="AE6">
-        <v>1.08</v>
-      </c>
-      <c r="AF6">
+      <c r="AG6">
         <v>2.25</v>
       </c>
-      <c r="AG6">
-        <v>1.57</v>
-      </c>
       <c r="AH6">
-        <v>11</v>
+        <v>4.95</v>
       </c>
       <c r="AI6">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>83</v>
@@ -1363,76 +1363,76 @@
         <v>82</v>
       </c>
       <c r="L7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="M7">
-        <v>3.56</v>
+        <v>2.81</v>
       </c>
       <c r="N7">
-        <v>2.88</v>
+        <v>3.73</v>
       </c>
       <c r="O7">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2.5</v>
+      </c>
+      <c r="R7">
+        <v>1.65</v>
+      </c>
+      <c r="S7">
+        <v>2.16</v>
+      </c>
+      <c r="T7">
+        <v>3.9</v>
+      </c>
+      <c r="U7">
+        <v>1.19</v>
+      </c>
+      <c r="V7">
+        <v>9</v>
+      </c>
+      <c r="W7">
+        <v>1.02</v>
+      </c>
+      <c r="X7">
+        <v>1.12</v>
+      </c>
+      <c r="Y7">
+        <v>5.7</v>
+      </c>
+      <c r="Z7">
+        <v>1.5</v>
+      </c>
+      <c r="AA7">
+        <v>2.37</v>
+      </c>
+      <c r="AB7">
+        <v>2.73</v>
+      </c>
+      <c r="AC7">
+        <v>1.4</v>
+      </c>
+      <c r="AD7">
+        <v>5.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>2.25</v>
+      </c>
+      <c r="AG7">
+        <v>1.57</v>
+      </c>
+      <c r="AH7">
         <v>11</v>
       </c>
-      <c r="Q7">
-        <v>2.25</v>
-      </c>
-      <c r="R7">
-        <v>1.3</v>
-      </c>
-      <c r="S7">
-        <v>3.4</v>
-      </c>
-      <c r="T7">
-        <v>2.5</v>
-      </c>
-      <c r="U7">
-        <v>1.5</v>
-      </c>
-      <c r="V7">
-        <v>6</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
-      </c>
-      <c r="Z7">
-        <v>1.22</v>
-      </c>
-      <c r="AA7">
-        <v>4.33</v>
-      </c>
-      <c r="AB7">
-        <v>1.57</v>
-      </c>
-      <c r="AC7">
-        <v>2.25</v>
-      </c>
-      <c r="AD7">
-        <v>2.38</v>
-      </c>
-      <c r="AE7">
-        <v>1.58</v>
-      </c>
-      <c r="AF7">
-        <v>1.57</v>
-      </c>
-      <c r="AG7">
-        <v>2.25</v>
-      </c>
-      <c r="AH7">
-        <v>4.75</v>
-      </c>
       <c r="AI7">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
         <v>83</v>
@@ -1640,7 +1640,7 @@
         <v>1.55</v>
       </c>
       <c r="AA9">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
         <v>2.15</v>
@@ -1664,7 +1664,7 @@
         <v>7.6</v>
       </c>
       <c r="AI9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
         <v>83</v>
@@ -1732,25 +1732,25 @@
         <v>1.62</v>
       </c>
       <c r="S10">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="U10">
         <v>1.17</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1.07</v>
       </c>
       <c r="Y10">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="Z10">
         <v>1.55</v>
@@ -1777,10 +1777,10 @@
         <v>1.64</v>
       </c>
       <c r="AH10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AI10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
         <v>83</v>
@@ -1943,76 +1943,76 @@
         <v>82</v>
       </c>
       <c r="L12">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>83</v>
@@ -2059,76 +2059,76 @@
         <v>82</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="s">
         <v>83</v>
@@ -2193,31 +2193,31 @@
         <v>2.88</v>
       </c>
       <c r="R14">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T14">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="U14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
         <v>6.5</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AA14">
         <v>3.4</v>
@@ -2238,10 +2238,10 @@
         <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH14">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="AI14">
         <v>1.11</v>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -133,6 +133,9 @@
     <t>06:00</t>
   </si>
   <si>
+    <t>08:30</t>
+  </si>
+  <si>
     <t>12:00</t>
   </si>
   <si>
@@ -157,18 +160,21 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -187,82 +193,91 @@
     <t>Avispa Fukuoka</t>
   </si>
   <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Mariehamn</t>
   </si>
   <si>
+    <t>Utsikten</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Utsikten</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
     <t>Huachipato</t>
   </si>
   <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
     <t>Kyoto Sanga</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Haka</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
     <t>Huracán</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Caxias</t>
   </si>
   <si>
-    <t>Guarani</t>
-  </si>
-  <si>
     <t>O'Higgins</t>
   </si>
   <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
     <t>incomplete</t>
+  </si>
+  <si>
+    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -629,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL14"/>
+  <dimension ref="A1:AL15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -756,16 +771,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -780,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L2">
         <v>2.72</v>
@@ -855,10 +870,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL2" s="3">
         <v>45859.25</v>
@@ -872,16 +887,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -896,88 +911,88 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L3">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="M3">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N3">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="P3">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V3">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>9</v>
       </c>
       <c r="Z3">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AD3">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AE3">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AH3">
-        <v>4.6</v>
+        <v>7.25</v>
       </c>
       <c r="AI3">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL3" s="3">
-        <v>45859.5</v>
+        <v>45859.35416666666</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -988,16 +1003,16 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1012,40 +1027,40 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L4">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="M4">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="O4">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Q4">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
         <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W4">
         <v>1.13</v>
@@ -1054,46 +1069,46 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA4">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC4">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD4">
         <v>2.38</v>
       </c>
       <c r="AE4">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AF4">
         <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH4">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL4" s="3">
-        <v>45859.58333333334</v>
+        <v>45859.5</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1101,19 +1116,19 @@
         <v>45859</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1128,43 +1143,43 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L5">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="M5">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="P5">
-        <v>13.25</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1173,40 +1188,40 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AB5">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AI5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL5" s="3">
         <v>45859.58333333334</v>
@@ -1217,19 +1232,19 @@
         <v>45859</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1244,85 +1259,85 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L6">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="M6">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="N6">
-        <v>2.33</v>
+        <v>3.73</v>
       </c>
       <c r="O6">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
         <v>1.13</v>
       </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
       <c r="Y6">
+        <v>5.7</v>
+      </c>
+      <c r="Z6">
+        <v>1.55</v>
+      </c>
+      <c r="AA6">
+        <v>2.31</v>
+      </c>
+      <c r="AB6">
+        <v>2.73</v>
+      </c>
+      <c r="AC6">
+        <v>1.4</v>
+      </c>
+      <c r="AD6">
+        <v>4.8</v>
+      </c>
+      <c r="AE6">
+        <v>1.15</v>
+      </c>
+      <c r="AF6">
+        <v>2.1</v>
+      </c>
+      <c r="AG6">
+        <v>1.67</v>
+      </c>
+      <c r="AH6">
         <v>11</v>
       </c>
-      <c r="Z6">
-        <v>1.15</v>
-      </c>
-      <c r="AA6">
-        <v>4.25</v>
-      </c>
-      <c r="AB6">
-        <v>1.6</v>
-      </c>
-      <c r="AC6">
-        <v>2.1</v>
-      </c>
-      <c r="AD6">
-        <v>2.6</v>
-      </c>
-      <c r="AE6">
-        <v>1.39</v>
-      </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
-      <c r="AG6">
-        <v>2.25</v>
-      </c>
-      <c r="AH6">
-        <v>4.95</v>
-      </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL6" s="3">
         <v>45859.58333333334</v>
@@ -1333,19 +1348,19 @@
         <v>45859</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1360,85 +1375,85 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L7">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="M7">
-        <v>2.81</v>
+        <v>3.56</v>
       </c>
       <c r="N7">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R7">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="T7">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="U7">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA7">
-        <v>2.37</v>
+        <v>3.74</v>
       </c>
       <c r="AB7">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC7">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AD7">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AF7">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AH7">
-        <v>11</v>
+        <v>5.15</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL7" s="3">
         <v>45859.58333333334</v>
@@ -1452,16 +1467,16 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1476,88 +1491,88 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L8">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="N8">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="O8">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
+        <v>1.5</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>1.13</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>11</v>
+      </c>
+      <c r="Z8">
         <v>1.22</v>
       </c>
-      <c r="V8">
-        <v>13</v>
-      </c>
-      <c r="W8">
-        <v>1.04</v>
-      </c>
-      <c r="X8">
-        <v>1.12</v>
-      </c>
-      <c r="Y8">
-        <v>5.75</v>
-      </c>
-      <c r="Z8">
-        <v>1.6</v>
-      </c>
       <c r="AA8">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB8">
-        <v>2.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AF8">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AH8">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AI8">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL8" s="3">
-        <v>45859.79166666666</v>
+        <v>45859.58333333334</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1568,16 +1583,16 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1592,88 +1607,88 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L9">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V9">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y9">
         <v>5.75</v>
       </c>
       <c r="Z9">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AC9">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AD9">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH9">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AI9">
         <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL9" s="3">
-        <v>45859.8125</v>
+        <v>45859.79166666666</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1681,19 +1696,19 @@
         <v>45859</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1708,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L10">
         <v>2.84</v>
@@ -1723,34 +1738,34 @@
         <v>1.95</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
       </c>
       <c r="R10">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S10">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T10">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V10">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y10">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="Z10">
         <v>1.55</v>
@@ -1765,28 +1780,28 @@
         <v>1.53</v>
       </c>
       <c r="AD10">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AE10">
         <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AG10">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AH10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL10" s="3">
         <v>45859.8125</v>
@@ -1800,16 +1815,16 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1824,88 +1839,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L11">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="N11">
-        <v>2.55</v>
+        <v>3.72</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="P11">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U11">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>6.35</v>
       </c>
       <c r="Z11">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AA11">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD11">
-        <v>3.65</v>
+        <v>5.15</v>
       </c>
       <c r="AE11">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AH11">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AI11">
         <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL11" s="3">
-        <v>45859.83333333334</v>
+        <v>45859.8125</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1916,16 +1931,16 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1940,88 +1955,88 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL12" s="3">
-        <v>45859.88541666666</v>
+        <v>45859.83333333334</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2029,19 +2044,19 @@
         <v>45859</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2056,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L13">
         <v>1.83</v>
@@ -2131,10 +2146,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL13" s="3">
         <v>45859.88541666666</v>
@@ -2148,16 +2163,16 @@
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2172,87 +2187,203 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>45859.88541666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="2">
+        <v>45859</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15">
         <v>1.64</v>
       </c>
-      <c r="M14">
+      <c r="M15">
         <v>3.5</v>
       </c>
-      <c r="N14">
+      <c r="N15">
         <v>4.5</v>
       </c>
-      <c r="O14">
+      <c r="O15">
         <v>1.57</v>
       </c>
-      <c r="P14">
+      <c r="P15">
         <v>8.9</v>
       </c>
-      <c r="Q14">
+      <c r="Q15">
         <v>2.88</v>
       </c>
-      <c r="R14">
-        <v>1.35</v>
-      </c>
-      <c r="S14">
-        <v>2.76</v>
-      </c>
-      <c r="T14">
-        <v>2.89</v>
-      </c>
-      <c r="U14">
-        <v>1.36</v>
-      </c>
-      <c r="V14">
-        <v>6.5</v>
-      </c>
-      <c r="W14">
-        <v>1.07</v>
-      </c>
-      <c r="X14">
-        <v>1</v>
-      </c>
-      <c r="Y14">
+      <c r="R15">
+        <v>1.32</v>
+      </c>
+      <c r="S15">
+        <v>3.3</v>
+      </c>
+      <c r="T15">
+        <v>2.5</v>
+      </c>
+      <c r="U15">
+        <v>1.48</v>
+      </c>
+      <c r="V15">
+        <v>5.5</v>
+      </c>
+      <c r="W15">
+        <v>1.11</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
         <v>10</v>
       </c>
-      <c r="Z14">
-        <v>1.25</v>
-      </c>
-      <c r="AA14">
-        <v>3.4</v>
-      </c>
-      <c r="AB14">
+      <c r="Z15">
+        <v>1.17</v>
+      </c>
+      <c r="AA15">
+        <v>3.9</v>
+      </c>
+      <c r="AB15">
         <v>1.88</v>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <v>1.82</v>
       </c>
-      <c r="AD14">
-        <v>3.28</v>
-      </c>
-      <c r="AE14">
-        <v>1.3</v>
-      </c>
-      <c r="AF14">
-        <v>1.8</v>
-      </c>
-      <c r="AG14">
-        <v>2.05</v>
-      </c>
-      <c r="AH14">
-        <v>6.75</v>
-      </c>
-      <c r="AI14">
-        <v>1.11</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AD15">
+        <v>2.74</v>
+      </c>
+      <c r="AE15">
+        <v>1.42</v>
+      </c>
+      <c r="AF15">
+        <v>1.61</v>
+      </c>
+      <c r="AG15">
+        <v>2.1</v>
+      </c>
+      <c r="AH15">
+        <v>5</v>
+      </c>
+      <c r="AI15">
+        <v>1.14</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45859.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-21.xlsx
+++ b/jogos_2025-07-21.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,63 +1030,63 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>1.2</v>
@@ -1095,44 +1095,44 @@
         <v>4.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
         <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['45', '82']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45859.5</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,63 +1159,63 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
       </c>
       <c r="W6" t="n">
         <v>1.2</v>
@@ -1224,44 +1224,44 @@
         <v>4.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AA6" t="n">
         <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['45', '82']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.57</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AI6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45859.5</v>
@@ -1314,46 +1314,46 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="O7" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
         <v>1.53</v>
@@ -1362,13 +1362,13 @@
         <v>4.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC7" t="n">
         <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45859.54166666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,91 +1417,91 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45859.54166666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45859.54166666666</v>
@@ -1665,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.79</v>
+        <v>10.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>3.09</v>
+        <v>4.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.52</v>
+        <v>2.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['43', '89', '90+3']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>4.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45859.5625</v>
@@ -1794,35 +1794,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.5</v>
+        <v>3.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
-        <v>4.33</v>
+        <v>3.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.55</v>
+        <v>3.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['43', '89', '90+3']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.3</v>
+        <v>2.52</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45859.5625</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['3', '52', '55']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['87']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45859.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['31', '55']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['3', '52', '55']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45859.58333333334</v>
@@ -2181,35 +2181,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.85</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA14" t="n">
         <v>3.1</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['31', '55']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45859.58333333334</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2335,10 +2335,10 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="M15" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="N15" t="n">
-        <v>3.23</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['21', '87']</t>
+          <t>['90', '90+4']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45859.58333333334</v>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2471,87 +2471,87 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['90', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45859.58333333334</v>
@@ -2865,58 +2865,58 @@
         <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X19" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.93</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45859.64583333334</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>3.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.99</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['12', '42']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['83', '60']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.35</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45859.8125</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3238,76 +3238,76 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.72</v>
-      </c>
       <c r="M22" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.37</v>
+        <v>2.81</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>4.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="T22" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.15</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['12', '42']</t>
+          <t>['83', '60']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45859.8125</v>
